--- a/exports/TIINDIA_full_report.xlsx
+++ b/exports/TIINDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.61</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44588.38541666666</v>
+        <v>44588.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>1694.75</v>
+        <v>1676</v>
       </c>
       <c r="I2" t="n">
         <v>1677.966585195104</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.14</v>
+        <v>-7.18</v>
       </c>
       <c r="L2" t="n">
         <v>8.48</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44596.55208333334</v>
+        <v>44599.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1785</v>
+        <v>1845.95</v>
       </c>
       <c r="I3" t="n">
         <v>1801.982631254586</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.5</v>
+        <v>-10.14</v>
       </c>
       <c r="L3" t="n">
-        <v>8.529999999999999</v>
+        <v>11.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.92</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1696.1</v>
+        <v>1602.85</v>
       </c>
       <c r="I4" t="n">
         <v>1683.655700785774</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.119999999999999</v>
+        <v>-13.17</v>
       </c>
       <c r="L4" t="n">
-        <v>8.69</v>
+        <v>13.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.83</v>
+        <v>5.55</v>
       </c>
       <c r="O4" t="n">
         <v>0.84</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.35</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44642.38541666666</v>
+        <v>44642.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>1591.3</v>
+        <v>1605.1</v>
       </c>
       <c r="I5" t="n">
         <v>1594.982323652416</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>0.72</v>
+        <v>-0.14</v>
       </c>
       <c r="L5" t="n">
         <v>6.62</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.86</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44691.55208333334</v>
+        <v>44692.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1835</v>
+        <v>1678.75</v>
       </c>
       <c r="I6" t="n">
         <v>1754.589892933537</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>14.32</v>
+        <v>4.59</v>
       </c>
       <c r="L6" t="n">
         <v>2.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.65</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>5.57</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1.91</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.68</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.38541666666</v>
+        <v>44736.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1569.3</v>
+        <v>1594.95</v>
       </c>
       <c r="I7" t="n">
         <v>1578.809610285942</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>6.52</v>
+        <v>4.99</v>
       </c>
       <c r="L7" t="n">
         <v>7.59</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2080</v>
+        <v>2019.95</v>
       </c>
       <c r="I8" t="n">
         <v>2024.984195678906</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>30.41</v>
+        <v>26.65</v>
       </c>
       <c r="L8" t="n">
         <v>1.89</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.37</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2117.05</v>
+        <v>2220.1</v>
       </c>
       <c r="I9" t="n">
         <v>2188.950745723769</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.81</v>
+        <v>-9.91</v>
       </c>
       <c r="L9" t="n">
-        <v>5.29</v>
+        <v>11.2</v>
       </c>
       <c r="M9" t="n">
         <v>0.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>3.78</v>
       </c>
       <c r="O9" t="n">
         <v>-2.86</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.62</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44796.55208333334</v>
+        <v>44797.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2095</v>
+        <v>2065.6</v>
       </c>
       <c r="I10" t="n">
         <v>2091.50289163637</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.63</v>
+        <v>-6.96</v>
       </c>
       <c r="L10" t="n">
-        <v>6.98</v>
+        <v>7.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.69</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2150</v>
+        <v>2250.75</v>
       </c>
       <c r="I11" t="n">
         <v>2216.446100092332</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.09</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>5.25</v>
+        <v>9.65</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="N11" t="n">
-        <v>4.28</v>
+        <v>5.53</v>
       </c>
       <c r="O11" t="n">
         <v>-1.77</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2560</v>
+        <v>2505.75</v>
       </c>
       <c r="I12" t="n">
         <v>2524.949346783294</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>13.74</v>
+        <v>11.33</v>
       </c>
       <c r="L12" t="n">
         <v>3.27</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44825.38541666666</v>
+        <v>44825.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>2728.65</v>
+        <v>2744</v>
       </c>
       <c r="I13" t="n">
         <v>2742.615673859152</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.9</v>
+        <v>-9.51</v>
       </c>
       <c r="L13" t="n">
         <v>10.55</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44830.55208333334</v>
+        <v>44831.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2650</v>
+        <v>2518</v>
       </c>
       <c r="I14" t="n">
         <v>2543.065826569423</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.43</v>
+        <v>-8.24</v>
       </c>
       <c r="L14" t="n">
-        <v>3.79</v>
+        <v>9.77</v>
       </c>
       <c r="M14" t="n">
         <v>1.52</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.83</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44867.38541666666</v>
+        <v>44867.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2806.65</v>
+        <v>2855</v>
       </c>
       <c r="I15" t="n">
         <v>2824.445119628848</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.46</v>
+        <v>-13.38</v>
       </c>
       <c r="L15" t="n">
         <v>14.45</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2710</v>
+        <v>2568.4</v>
       </c>
       <c r="I16" t="n">
         <v>2701.910346131482</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.08</v>
+        <v>-10.04</v>
       </c>
       <c r="L16" t="n">
-        <v>5.91</v>
+        <v>12.25</v>
       </c>
       <c r="M16" t="n">
         <v>0.53</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>12.8</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2773.65</v>
+        <v>2790</v>
       </c>
       <c r="I17" t="n">
         <v>2776.287448965621</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.99</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>9.34</v>
+        <v>10.34</v>
       </c>
       <c r="M17" t="n">
         <v>2.98</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>12.2</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44923.55208333334</v>
+        <v>44924.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2780</v>
+        <v>2682</v>
       </c>
       <c r="I18" t="n">
         <v>2748.565882717359</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.36</v>
+        <v>-3.87</v>
       </c>
       <c r="L18" t="n">
-        <v>4.09</v>
+        <v>4.48</v>
       </c>
       <c r="M18" t="n">
         <v>1.39</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44959.38541666666</v>
+        <v>44959.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2575</v>
+        <v>2729.9</v>
       </c>
       <c r="I19" t="n">
         <v>2716.203262734055</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>3.99</v>
+        <v>-1.79</v>
       </c>
       <c r="L19" t="n">
         <v>5.61</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.6</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44971.55208333334</v>
+        <v>44972.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2478.5</v>
+        <v>2411.1</v>
       </c>
       <c r="I20" t="n">
         <v>2414.110355749379</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.210000000000001</v>
+        <v>-11.68</v>
       </c>
       <c r="L20" t="n">
-        <v>10.14</v>
+        <v>11.79</v>
       </c>
       <c r="M20" t="n">
         <v>1.21</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>10.57</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44984.38541666666</v>
+        <v>44984.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>2542.35</v>
+        <v>2640</v>
       </c>
       <c r="I21" t="n">
         <v>2584.300061241323</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.44</v>
+        <v>-9.49</v>
       </c>
       <c r="L21" t="n">
-        <v>7.72</v>
+        <v>13.85</v>
       </c>
       <c r="M21" t="n">
         <v>0.82</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>2580.4</v>
+        <v>2546.4</v>
       </c>
       <c r="I22" t="n">
         <v>2559.603000821651</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.26</v>
+        <v>-3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="M22" t="n">
         <v>0.9</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45027.55208333334</v>
+        <v>45028.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2576</v>
+        <v>2631.95</v>
       </c>
       <c r="I23" t="n">
         <v>2630.896601105861</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.16</v>
+        <v>-3.36</v>
       </c>
       <c r="L23" t="n">
         <v>4.07</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2629</v>
+        <v>2580.25</v>
       </c>
       <c r="I24" t="n">
         <v>2580.354463845084</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.11</v>
+        <v>-1.96</v>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="M24" t="n">
         <v>0.7</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.14</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45054.55208333334</v>
+        <v>45055.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2602.95</v>
+        <v>2678.3</v>
       </c>
       <c r="I25" t="n">
         <v>2650.204489540704</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.88</v>
+        <v>-3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>3.48</v>
+        <v>4.61</v>
       </c>
       <c r="M25" t="n">
         <v>0.71</v>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>4.46</v>
       </c>
       <c r="O25" t="n">
         <v>-1.45</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.81</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45133.38541666666</v>
+        <v>45133.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>3135.05</v>
+        <v>3100</v>
       </c>
       <c r="I26" t="n">
         <v>3105.962608685425</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>78</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>17.05</v>
+        <v>15.75</v>
       </c>
       <c r="L26" t="n">
         <v>2.44</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.01</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45169.55208333334</v>
+        <v>45170.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>2875</v>
+        <v>2980.3</v>
       </c>
       <c r="I27" t="n">
         <v>2911.753902533874</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>7.26</v>
+        <v>3.86</v>
       </c>
       <c r="L27" t="n">
         <v>2.42</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>7.27</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3358</v>
+        <v>3214.75</v>
       </c>
       <c r="I28" t="n">
         <v>3338.756951537838</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>12.67</v>
+        <v>7.87</v>
       </c>
       <c r="L28" t="n">
         <v>3.56</v>
       </c>
       <c r="M28" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="N28" t="n">
         <v>8.6</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.77</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2925.15</v>
+        <v>3055.85</v>
       </c>
       <c r="I29" t="n">
         <v>3052.852568386123</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K29" t="n">
-        <v>9.01</v>
+        <v>4.94</v>
       </c>
       <c r="L29" t="n">
         <v>7.33</v>
@@ -2094,7 +2441,7 @@
         <v>1.19</v>
       </c>
       <c r="N29" t="n">
-        <v>3.41</v>
+        <v>4.88</v>
       </c>
       <c r="O29" t="n">
         <v>-3.05</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45260.55208333334</v>
+        <v>45261.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>3355.05</v>
+        <v>3289.8</v>
       </c>
       <c r="I30" t="n">
         <v>3335.328382378904</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
-        <v>9.789999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="L30" t="n">
         <v>3.95</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45268.38541666666</v>
+        <v>45268.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>3458.4</v>
+        <v>3578</v>
       </c>
       <c r="I31" t="n">
         <v>3539.146361424174</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.12</v>
+        <v>-8.76</v>
       </c>
       <c r="L31" t="n">
-        <v>7.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>0.55</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.81</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45324.38541666666</v>
+        <v>45324.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>3668</v>
+        <v>3626</v>
       </c>
       <c r="I32" t="n">
         <v>3662.720836916932</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>55.83333333333334</v>
+        <v>56</v>
       </c>
       <c r="K32" t="n">
-        <v>2.52</v>
+        <v>1.34</v>
       </c>
       <c r="L32" t="n">
         <v>4.98</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.07</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45342.38541666666</v>
+        <v>45342.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>3702.75</v>
+        <v>3724</v>
       </c>
       <c r="I33" t="n">
         <v>3714.210708463751</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.12</v>
+        <v>-2.7</v>
       </c>
       <c r="L33" t="n">
         <v>3.31</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.73</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45387.55208333334</v>
+        <v>45390.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3600</v>
+        <v>3572.1</v>
       </c>
       <c r="I34" t="n">
         <v>3586.394883593865</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.33</v>
+        <v>-4.08</v>
       </c>
       <c r="L34" t="n">
         <v>8.74</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.01</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3650</v>
+        <v>3661.85</v>
       </c>
       <c r="I35" t="n">
         <v>3654.671418685827</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.18</v>
+        <v>-2.51</v>
       </c>
       <c r="L35" t="n">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="M35" t="n">
         <v>0.8</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.25</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45426.38541666666</v>
+        <v>45426.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>3807.35</v>
+        <v>3752.8</v>
       </c>
       <c r="I36" t="n">
         <v>3788.3624900879</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>3.97</v>
+        <v>2.48</v>
       </c>
       <c r="L36" t="n">
         <v>1.36</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3905.05</v>
+        <v>3973.2</v>
       </c>
       <c r="I37" t="n">
         <v>3923.096179758408</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.06</v>
+        <v>-5.87</v>
       </c>
       <c r="L37" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="M37" t="n">
         <v>3.37</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>10.16</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45464.38541666666</v>
+        <v>45464.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>4149.8</v>
+        <v>3986</v>
       </c>
       <c r="I38" t="n">
         <v>4009.52001631952</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>4.44</v>
+        <v>0.32</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="M38" t="n">
         <v>0.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>11.75</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45483.38541666666</v>
+        <v>45483.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>4323.75</v>
+        <v>4681.7</v>
       </c>
       <c r="I39" t="n">
         <v>4421.285107170803</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.470000000000001</v>
+        <v>-17.45</v>
       </c>
       <c r="L39" t="n">
-        <v>13.9</v>
+        <v>17.45</v>
       </c>
       <c r="M39" t="n">
         <v>0.97</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>14.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>4005.25</v>
+        <v>3981</v>
       </c>
       <c r="I40" t="n">
         <v>3986.953679933511</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K40" t="n">
-        <v>-14.45</v>
+        <v>-14.97</v>
       </c>
       <c r="L40" t="n">
-        <v>14.95</v>
+        <v>14.99</v>
       </c>
       <c r="M40" t="n">
         <v>1.96</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>4102.05</v>
+        <v>4245</v>
       </c>
       <c r="I41" t="n">
         <v>4137.44936525778</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>62.83333333333334</v>
+        <v>63</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.04</v>
+        <v>-6.63</v>
       </c>
       <c r="L41" t="n">
-        <v>6.46</v>
+        <v>11.8</v>
       </c>
       <c r="M41" t="n">
         <v>1.55</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.81</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>4083.95</v>
+        <v>3956.1</v>
       </c>
       <c r="I42" t="n">
         <v>4049.430905815763</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.79</v>
+        <v>-6.81</v>
       </c>
       <c r="L42" t="n">
-        <v>4.76</v>
+        <v>6.91</v>
       </c>
       <c r="M42" t="n">
         <v>1.85</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.33</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45580.38541666666</v>
+        <v>45580.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>4287.95</v>
+        <v>4325</v>
       </c>
       <c r="I43" t="n">
         <v>4318.187717332366</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.32</v>
       </c>
       <c r="L43" t="n">
-        <v>8.960000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="M43" t="n">
         <v>1.38</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.92</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45600.55208333334</v>
+        <v>45601.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>4312.05</v>
+        <v>4112.15</v>
       </c>
       <c r="I44" t="n">
         <v>4296.603619772314</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.3</v>
+        <v>-4.92</v>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>5.04</v>
       </c>
       <c r="M44" t="n">
         <v>1.21</v>
       </c>
       <c r="N44" t="n">
-        <v>3.09</v>
+        <v>3.47</v>
       </c>
       <c r="O44" t="n">
         <v>2.63</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.17</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>3652</v>
+        <v>3762.45</v>
       </c>
       <c r="I45" t="n">
         <v>3666.67471132341</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
-        <v>11.19</v>
+        <v>8.5</v>
       </c>
       <c r="L45" t="n">
         <v>4.57</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.1</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45656.38541666666</v>
+        <v>45656.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>3578.05</v>
+        <v>3535.05</v>
       </c>
       <c r="I46" t="n">
         <v>3554.834442190521</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.9</v>
+        <v>-6.04</v>
       </c>
       <c r="L46" t="n">
         <v>6.6</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.18</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2650.95</v>
+        <v>2735.9</v>
       </c>
       <c r="I47" t="n">
         <v>2659.324514634362</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="K47" t="n">
-        <v>25.01</v>
+        <v>22.61</v>
       </c>
       <c r="L47" t="n">
         <v>4.49</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.37</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45741.55208333334</v>
+        <v>45742.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2767</v>
+        <v>2716.05</v>
       </c>
       <c r="I48" t="n">
         <v>2720.385701331124</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>1.14</v>
+        <v>-0.73</v>
       </c>
       <c r="L48" t="n">
         <v>5.7</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45770.38541666666</v>
+        <v>45770.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>2661</v>
+        <v>2672</v>
       </c>
       <c r="I49" t="n">
         <v>2661.926966929498</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="L49" t="n">
         <v>3.95</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>6.57</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>2978.9</v>
+        <v>2940.1</v>
       </c>
       <c r="I50" t="n">
         <v>2951.720949862309</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>11.49</v>
+        <v>10.03</v>
       </c>
       <c r="L50" t="n">
         <v>4.48</v>
       </c>
       <c r="M50" t="n">
-        <v>1.19</v>
+        <v>2.31</v>
       </c>
       <c r="N50" t="n">
         <v>4.34</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.36</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>2990.8</v>
+        <v>3007.5</v>
       </c>
       <c r="I51" t="n">
         <v>2995.258312906087</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.72</v>
+        <v>-2.29</v>
       </c>
       <c r="L51" t="n">
         <v>2.84</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.91</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45845.55208333334</v>
+        <v>45846.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>2940</v>
+        <v>2906.4</v>
       </c>
       <c r="I52" t="n">
         <v>2934.322684692789</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.24</v>
+        <v>-3.36</v>
       </c>
       <c r="L52" t="n">
-        <v>3.01</v>
+        <v>4.24</v>
       </c>
       <c r="M52" t="n">
         <v>0.47</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.47</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45875.38541666666</v>
+        <v>45875.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>2937.5</v>
+        <v>2976.9</v>
       </c>
       <c r="I53" t="n">
         <v>2950.709569548774</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.07</v>
+        <v>-2.43</v>
       </c>
       <c r="L53" t="n">
         <v>3.39</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.79</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>3022.9</v>
+        <v>2958.8</v>
       </c>
       <c r="I54" t="n">
         <v>3015.575509647994</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>1.55</v>
+        <v>-0.61</v>
       </c>
       <c r="L54" t="n">
         <v>3.31</v>
@@ -3519,7 +4166,7 @@
         <v>0.5</v>
       </c>
       <c r="N54" t="n">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="O54" t="n">
         <v>3.01</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7.73</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45901.38541666666</v>
+        <v>45901.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>3113</v>
+        <v>3150</v>
       </c>
       <c r="I55" t="n">
         <v>3119.994387727902</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.21</v>
+        <v>-6.46</v>
       </c>
       <c r="L55" t="n">
-        <v>5.28</v>
+        <v>6.53</v>
       </c>
       <c r="M55" t="n">
         <v>0.5</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>3233.2</v>
+        <v>3202</v>
       </c>
       <c r="I56" t="n">
         <v>3219.092289284053</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K56" t="n">
-        <v>2.64</v>
+        <v>1.65</v>
       </c>
       <c r="L56" t="n">
         <v>6.47</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.72</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46051.38541666666</v>
+        <v>46051.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>2295.7</v>
+        <v>2330</v>
       </c>
       <c r="I57" t="n">
         <v>2324.976489024417</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>125.8333333333333</v>
+        <v>126</v>
       </c>
       <c r="K57" t="n">
-        <v>28.3</v>
+        <v>27.23</v>
       </c>
       <c r="L57" t="n">
         <v>1.9</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>167</v>
+        <v>168</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.69</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46058.55208333334</v>
+        <v>46059.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2378</v>
+        <v>2278.7</v>
       </c>
       <c r="I58" t="n">
         <v>2322.023108287314</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>2.06</v>
+        <v>-2.2</v>
       </c>
       <c r="L58" t="n">
         <v>2.65</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>14.58</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46073.38541666666</v>
+        <v>46073.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>2540.8</v>
+        <v>2574.1</v>
       </c>
       <c r="I59" t="n">
         <v>2569.024138652693</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-11.5</v>
+        <v>-12.96</v>
       </c>
       <c r="L59" t="n">
-        <v>12.16</v>
+        <v>13.75</v>
       </c>
       <c r="M59" t="n">
         <v>0.82</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.04</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46091.55208333334</v>
+        <v>46092.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2652</v>
+        <v>2572.3</v>
       </c>
       <c r="I60" t="n">
         <v>2582.203852460041</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>3.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>2.4</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>10.39</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2562.6</v>
+        <v>2660.4</v>
       </c>
       <c r="I61" t="n">
         <v>2619.478483683086</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>0.38</v>
+        <v>-3.42</v>
       </c>
       <c r="L61" t="n">
-        <v>3.98</v>
+        <v>4.42</v>
       </c>
       <c r="M61" t="n">
         <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>3.35</v>
+        <v>4.49</v>
       </c>
       <c r="O61" t="n">
         <v>-3.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.67</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2936.3</v>
+        <v>2802</v>
       </c>
       <c r="I62" t="n">
         <v>2866.631574519836</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>10.37</v>
+        <v>5.32</v>
       </c>
       <c r="L62" t="n">
         <v>7.05</v>
@@ -3975,7 +4718,7 @@
         <v>2.65</v>
       </c>
       <c r="N62" t="n">
-        <v>4.09</v>
+        <v>4.64</v>
       </c>
       <c r="O62" t="n">
         <v>4.49</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>12.12</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>3006.7</v>
+        <v>3053.4</v>
       </c>
       <c r="I63" t="n">
         <v>3048.831427141155</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.31</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>9.33</v>
+        <v>10.64</v>
       </c>
       <c r="M63" t="n">
-        <v>0.43</v>
+        <v>1.24</v>
       </c>
       <c r="N63" t="n">
         <v>3.98</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.79</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46184.38541666666</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>3043</v>
+        <v>2981.1</v>
       </c>
       <c r="I64" t="n">
         <v>2994.845698452187</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.34</v>
+        <v>-2.37</v>
       </c>
       <c r="L64" t="n">
-        <v>2.07</v>
+        <v>2.99</v>
       </c>
       <c r="M64" t="n">
         <v>1.23</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.09</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46188.38541666666</v>
+        <v>46188.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>3221.5</v>
+        <v>3240</v>
       </c>
       <c r="I65" t="n">
         <v>3222.35155242567</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.06</v>
+        <v>-8.68</v>
       </c>
       <c r="L65" t="n">
-        <v>8.85</v>
+        <v>9.32</v>
       </c>
       <c r="M65" t="n">
         <v>1.53</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.34</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46197.55208333334</v>
+        <v>46198.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>3161.1</v>
+        <v>3093.8</v>
       </c>
       <c r="I66" t="n">
         <v>3120.333478840086</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.44</v>
+        <v>-4.51</v>
       </c>
       <c r="L66" t="n">
-        <v>2.44</v>
+        <v>4.78</v>
       </c>
       <c r="M66" t="n">
         <v>0.66</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.43</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>2756</v>
+        <v>2949.5</v>
       </c>
       <c r="I67" t="n">
         <v>2861.343953600859</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K67" t="n">
-        <v>10.92</v>
+        <v>4.66</v>
       </c>
       <c r="L67" t="n">
         <v>3.1</v>
@@ -4260,7 +5063,7 @@
         <v>1.96</v>
       </c>
       <c r="N67" t="n">
-        <v>2.38</v>
+        <v>7.62</v>
       </c>
       <c r="O67" t="n">
         <v>-2.88</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.14</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>2776</v>
+        <v>2759.4</v>
       </c>
       <c r="I68" t="n">
         <v>2762.07340165202</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.88</v>
+        <v>-6.45</v>
       </c>
       <c r="L68" t="n">
-        <v>6.57</v>
+        <v>6.76</v>
       </c>
       <c r="M68" t="n">
         <v>0.8</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.33</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>2320</v>
+        <v>2465.8</v>
       </c>
       <c r="I69" t="n">
         <v>2447.986023903499</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>15.92</v>
+        <v>10.64</v>
       </c>
       <c r="L69" t="n">
         <v>1.29</v>
@@ -4374,7 +5201,7 @@
         <v>0.89</v>
       </c>
       <c r="N69" t="n">
-        <v>1.77</v>
+        <v>6.16</v>
       </c>
       <c r="O69" t="n">
         <v>-0.9399999999999999</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>9.99</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>2391</v>
+        <v>2275.8</v>
       </c>
       <c r="I70" t="n">
         <v>2297.135820638166</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.03</v>
+        <v>-7.71</v>
       </c>
       <c r="L70" t="n">
-        <v>6.24</v>
+        <v>7.86</v>
       </c>
       <c r="M70" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="N70" t="n">
-        <v>2.92</v>
+        <v>5.77</v>
       </c>
       <c r="O70" t="n">
         <v>6.16</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>26</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.3</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125.8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.3</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.72</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.41</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.6</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.49</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.76</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.95</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="25">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.62</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="27">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
